--- a/data/trans_camb/IP16A06-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A06-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -631,12 +631,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 8,52</t>
+          <t>-16,62; 8,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-23,01; 0,0</t>
+          <t>-25,74; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -646,17 +646,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,58</t>
+          <t>0,0; 14,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 3,84</t>
+          <t>-9,61; 3,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 2,85</t>
+          <t>-10,1; 2,86</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,34</t>
+          <t>0,0; 10,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,87; 1,66</t>
+          <t>-17,47; 1,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,36; 0,0</t>
+          <t>-19,98; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 2,55</t>
+          <t>-7,15; 2,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 0,0</t>
+          <t>-9,84; 0,0</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -943,17 +943,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-33,28; 0,0</t>
+          <t>-27,31; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-30,84; 0,0</t>
+          <t>-33,73; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,71</t>
+          <t>0,0; 15,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 3,22</t>
+          <t>-12,82; 3,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 0,0</t>
+          <t>-15,9; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,35</t>
+          <t>0,0; 17,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,12; 0,0</t>
+          <t>-17,62; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-18,56; 0,0</t>
+          <t>-15,97; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 8,37</t>
+          <t>-3,63; 8,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 0,0</t>
+          <t>-9,18; 0,0</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,9</t>
+          <t>0,0; 19,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,28</t>
+          <t>0,0; 9,94</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 0,0</t>
+          <t>-14,64; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 16,24</t>
+          <t>-5,41; 18,61</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 6,17</t>
+          <t>-3,03; 5,95</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 0,0</t>
+          <t>-11,42; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 7,7</t>
+          <t>-5,63; 8,18</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 10,75</t>
+          <t>-3,5; 11,04</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 6,01</t>
+          <t>-3,55; 5,98</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 4,22</t>
+          <t>-4,13; 3,29</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 5,2</t>
+          <t>-4,12; 4,78</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 2,06</t>
+          <t>-2,84; 2,12</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 0,64</t>
+          <t>-3,56; 0,87</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 1,25</t>
+          <t>-3,45; 1,31</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 1,18</t>
+          <t>-3,64; 1,16</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 1,24</t>
+          <t>-2,32; 1,08</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 0,4</t>
+          <t>-2,72; 0,47</t>
         </is>
       </c>
     </row>
@@ -1965,22 +1965,22 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-89,66; 184,84</t>
+          <t>-89,82; 174,06</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 240,65</t>
+          <t>-99,03; 273,95</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-74,77; 148,45</t>
+          <t>-75,65; 113,53</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-87,76; 71,15</t>
+          <t>-88,57; 74,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A06-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A06-Provincia-trans_camb.xlsx
@@ -631,12 +631,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,62; 8,77</t>
+          <t>-16,74; 8,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,74; 0,0</t>
+          <t>-26,16; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -646,17 +646,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,71</t>
+          <t>0,0; 13,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 3,84</t>
+          <t>-10,03; 3,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 2,86</t>
+          <t>-10,21; 2,84</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,41</t>
+          <t>0,0; 10,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,47; 1,66</t>
+          <t>-18,09; 1,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,98; 0,0</t>
+          <t>-18,85; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 2,84</t>
+          <t>-8,34; 2,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,84; 0,0</t>
+          <t>-11,22; 0,0</t>
         </is>
       </c>
     </row>
@@ -943,17 +943,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-27,31; 0,0</t>
+          <t>-27,0; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-33,73; 0,0</t>
+          <t>-34,14; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,0</t>
+          <t>0,0; 15,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,82; 3,19</t>
+          <t>-13,77; 3,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,9; 0,0</t>
+          <t>-19,08; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,4</t>
+          <t>0,0; 19,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,62; 0,0</t>
+          <t>-19,35; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,97; 0,0</t>
+          <t>-20,94; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 8,71</t>
+          <t>-3,71; 8,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 0,0</t>
+          <t>-10,15; 0,0</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,84</t>
+          <t>0,0; 25,08</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,94</t>
+          <t>0,0; 11,78</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1577,22 +1577,22 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-14,64; 0,0</t>
+          <t>-11,05; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 18,61</t>
+          <t>-5,45; 20,42</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 0,0</t>
+          <t>-7,57; 0,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 5,95</t>
+          <t>-3,05; 6,23</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 0,0</t>
+          <t>-12,8; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 8,18</t>
+          <t>-7,47; 7,55</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 11,04</t>
+          <t>-3,53; 10,55</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 5,98</t>
+          <t>-3,53; 6,25</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 3,29</t>
+          <t>-4,17; 4,13</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 4,78</t>
+          <t>-3,16; 5,0</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 2,12</t>
+          <t>-2,6; 2,31</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 0,87</t>
+          <t>-3,48; 0,71</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 1,31</t>
+          <t>-3,52; 1,31</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 1,16</t>
+          <t>-3,68; 1,2</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 1,08</t>
+          <t>-2,27; 1,17</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 0,47</t>
+          <t>-2,77; 0,39</t>
         </is>
       </c>
     </row>
@@ -1965,22 +1965,22 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-89,82; 174,06</t>
+          <t>-90,89; 192,83</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-99,03; 273,95</t>
+          <t>-100,0; 215,15</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-75,65; 113,53</t>
+          <t>-75,71; 118,14</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-88,57; 74,59</t>
+          <t>-90,74; 48,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A06-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A06-Provincia-trans_camb.xlsx
@@ -513,19 +513,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  tranquilizantes, relajantes</t>
+          <t>Menores que consumieron  tranquilizantes, relajantes</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,55</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-0,83</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-5,13</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,55</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,74; 8,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-26,16; 0,0</t>
+          <t>0,0; 12,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-15,93; 8,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,22</t>
+          <t>-23,01; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 3,82</t>
+          <t>-8,17; 3,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 2,84</t>
+          <t>-9,5; 2,85</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-16,23%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-4,39</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-6,02</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>2,05</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-4,39</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-6,02</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,44</t>
+          <t>-17,87; 1,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-20,36; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,09; 1,64</t>
+          <t>0,0; 10,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,85; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 2,72</t>
+          <t>-7,86; 2,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 0,0</t>
+          <t>-11,34; 0,0</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-72,95%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-72,95%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,92</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-6,8</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-6,8</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,92</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-27,0; 0,0</t>
+          <t>0,0; 15,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-34,14; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,59</t>
+          <t>-33,28; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-30,84; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,77; 3,23</t>
+          <t>-14,29; 3,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,08; 0,0</t>
+          <t>-17,71; 0,0</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-3,61</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-3,61</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>5,84</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,61</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-3,61</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,64</t>
+          <t>-15,12; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-18,56; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,35; 0,0</t>
+          <t>0,0; 17,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,94; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 8,76</t>
+          <t>-3,63; 8,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 0,0</t>
+          <t>-9,21; 0,0</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,17 +1217,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4,76</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>4,76</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 24,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,78</t>
+          <t>0,0; 11,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1293,17 +1293,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-2,73</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1,89</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-2,73</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-14,0; 0,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,44; 16,24</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 20,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 0,0</t>
+          <t>-7,59; 0,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 6,23</t>
+          <t>-3,04; 6,17</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>69,12%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>69,12%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>0,93</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>0,19</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>-2,52</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>1,37</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>0,93</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>0,19</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-12,8; 0,0</t>
+          <t>-3,5; 10,75</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 7,55</t>
+          <t>-3,57; 6,01</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 10,55</t>
+          <t>-12,46; 0,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 6,25</t>
+          <t>-7,17; 7,7</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 4,13</t>
+          <t>-4,1; 4,22</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 5,0</t>
+          <t>-3,34; 5,2</t>
         </is>
       </c>
     </row>
@@ -1761,22 +1761,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>52,71%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10,55%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>54,45%</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>52,71%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>10,55%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1841,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-0,84</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-0,98</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>-0,05</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>-0,93</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-0,84</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-0,98</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 2,31</t>
+          <t>-3,32; 1,25</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 0,71</t>
+          <t>-3,76; 1,18</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 1,31</t>
+          <t>-2,76; 2,06</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 1,2</t>
+          <t>-3,7; 0,64</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,17</t>
+          <t>-2,28; 1,24</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 0,39</t>
+          <t>-2,65; 0,4</t>
         </is>
       </c>
     </row>
@@ -1917,22 +1917,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-37,62%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-43,78%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>-3,31%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>-56,94%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-37,62%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-43,78%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-89,66; 184,84</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 240,65</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-90,89; 192,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 215,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-75,71; 118,14</t>
+          <t>-74,77; 148,45</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-90,74; 48,05</t>
+          <t>-87,76; 71,15</t>
         </is>
       </c>
     </row>
